--- a/Data/ArthurHeimCareerDataFr.xlsx
+++ b/Data/ArthurHeimCareerDataFr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurheim/Library/CloudStorage/Dropbox/Travail_encrypted_decrypted/PHD/career/Data_DrivenResume/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951695AC-5611-0A48-8089-66ACEF6FB614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C25AB6-A7B2-084D-96FB-891C2F6CA225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4700" yWindow="3200" windowWidth="27240" windowHeight="19200" activeTab="7" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
   </bookViews>
@@ -21,9 +21,10 @@
     <sheet name="Thesis" sheetId="5" r:id="rId6"/>
     <sheet name="Research" sheetId="9" r:id="rId7"/>
     <sheet name="PaperDetails" sheetId="11" r:id="rId8"/>
-    <sheet name="ResearchProjects" sheetId="10" r:id="rId9"/>
-    <sheet name="conferences" sheetId="6" r:id="rId10"/>
-    <sheet name="teaching" sheetId="4" r:id="rId11"/>
+    <sheet name="Distinctions" sheetId="12" r:id="rId9"/>
+    <sheet name="ResearchProjects" sheetId="10" r:id="rId10"/>
+    <sheet name="conferences" sheetId="6" r:id="rId11"/>
+    <sheet name="teaching" sheetId="4" r:id="rId12"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="305">
   <si>
     <t>Degree</t>
   </si>
@@ -843,148 +844,166 @@
     <t>Licence - Économie appliquée</t>
   </si>
   <si>
+    <t>[\faAngleDoubleRight] \underline{Mémoire}:  \emph{Public sector as a shelter ? The impact of graduating in a recession on selection into public employment.}\\
+\underline{Directeur de mémoire}: \href{https://www.parisschoolofeconomics.eu/en/maurin-eric/}{Eric Maurin} \\
+\underline{Jury}: \href{https://sites.google.com/site/barbarapetrongolo/home}{Barbara Petrongolo}</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
+    <t>Évaluation des politiques publiques</t>
+  </si>
+  <si>
+    <t>Méthodes d'évaluations des politiques de santé</t>
+  </si>
+  <si>
+    <t>Évaluation des politiques de lutte contre la pauvreté</t>
+  </si>
+  <si>
+    <t>Reliance: Éxpérimentation aléatoire d'un programme d'activation de familles monoparentales au RSA longue durée</t>
+  </si>
+  <si>
+    <t>POSAJE: Éxpérimentation multi-bras pour favoriser l'accès aux modes d'accueil formels</t>
+  </si>
+  <si>
+    <t>ISAJE: Investissement social dans l'accueil du jeune enfant</t>
+  </si>
+  <si>
+    <t>MESAJE: Mesures des effets sociaux de l'accueil du jeune enfant</t>
+  </si>
+  <si>
+    <t>ADAJE: Aide à la décision pour l'accueil du jeune enfant</t>
+  </si>
+  <si>
+    <t>Bourse ERC - MADPART - avec Julien Combe. Déploiement d'algorithmes d'affectation des places en crèche et expérimentation aléatoire d'information détaillées aux familles sur leur fonctionnement. Analyse du rôle des options alternative des parents dans les choix</t>
+  </si>
+  <si>
+    <t>VISAJE: Valeurs individuelles et sociales de l'accueil du jeune enfant</t>
+  </si>
+  <si>
+    <t>Conférence de consensus: Le redoublement et ses alternatives</t>
+  </si>
+  <si>
+    <t>Les inégalités scolaires d'origines sociales</t>
+  </si>
+  <si>
+    <t>Recherche reproductible, intégration avec \LaTeX, présentations, sites web</t>
+  </si>
+  <si>
+    <t>Rapports et présentations</t>
+  </si>
+  <si>
+    <t>Formatage des données, programmation fonctionnelle</t>
+  </si>
+  <si>
+    <t>Contrôle de version, recherche collaborative</t>
+  </si>
+  <si>
+    <t>Manipulation de données et économétrie</t>
+  </si>
+  <si>
+    <t>Programmation orientée objet et science des données</t>
+  </si>
+  <si>
+    <t>Manipulation et visualisation de données ; économétrie, Machine learning</t>
+  </si>
+  <si>
+    <t>Paris School of Economics - EHESS, ED-465 Paris I, Panthéon Sorbonne</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>Association française des économistes de la population</t>
+  </si>
+  <si>
+    <t>Jun 2024</t>
+  </si>
+  <si>
+    <t>Mai 2025</t>
+  </si>
+  <si>
+    <t>Conférence | AFEPOP 2025</t>
+  </si>
+  <si>
+    <t>Seminar | J-pal \&amp; IPP</t>
+  </si>
+  <si>
+    <t>Seminar | Public economics</t>
+  </si>
+  <si>
+    <t>OECD expert group |  ‘What standards of evidence are needed for policy design, implementation and evaluation’</t>
+  </si>
+  <si>
+    <t>International conference | Using educational research and innovation to address inequality and achievement gaps in education</t>
+  </si>
+  <si>
+    <t>Conference | Evaluating public policies</t>
+  </si>
+  <si>
+    <t>Seminar | education policies</t>
+  </si>
+  <si>
+    <t>Conférence | Social investment for the youths</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> \emph{Income support strategies to reduce inequalities : Insights from France}</t>
+  </si>
+  <si>
+    <t>\emph{Demand for international standards of evidence : thoughts from a French perspective}</t>
+  </si>
+  <si>
+    <t>Institut national des études teritoriales (INET)</t>
+  </si>
+  <si>
+    <t>Institut de la gestion publique et du développement économique (IGPDE)</t>
+  </si>
+  <si>
+    <t>École nationale supérieure de la sécurité sociale (EN3S)</t>
+  </si>
+  <si>
+    <t>Conduire l’évaluation des effets de la stratégie nationale de prévention et de lutte contre la pauvreté, sous la présidence de Louis Schweitzer.</t>
+  </si>
+  <si>
+    <t>Proposer des actions relevant de politiques publiques centrées sur le développement, l’épanouissement et les acquisitions du jeune enfant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nature Human Behaviour</t>
+  </si>
+  <si>
+    <t>{\bf Forthcoming}</t>
+  </si>
+  <si>
+    <t>{\bf R \&amp; R} European Economic Review</t>
+  </si>
+  <si>
+    <t>{\bf R \&amp; R} Nature Human Behaviour</t>
+  </si>
+  <si>
+    <t>Social investment and the changing face of poverty: Essays on the design and evaluation of family and social policies in France</t>
+  </si>
+  <si>
+    <t>Cour des comptes</t>
+  </si>
+  <si>
+    <t>1er prix ex-æequo</t>
+  </si>
+  <si>
+    <t>Remis par le 1er président de la Cour le 27 Mai 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">[\faAngleDoubleRight] \underline{Thèse}: \emph{\href{https://hal.science/tel-04801852v1}{Social investment and the changing face of poverty: Essays on the design and evaluation of social and family policies in France}} \\
  \underline{Directeur de thèse:} \href{https://www.parisschoolofeconomics.eu/en/gurgand-marc/}{Marc Gurgand}  \\
  \underline{ Jury}:  \href{http://www.anneboring.com/}{Anne Boring}, \href{https://sites.google.com/site/rafaellalive/}{Rafael Lalive}, \href{https://sites.google.com/view/camilleterrier/accueil}{Camille Terrier}, \href{https://www.parisschoolofeconomics.eu/en/macours-karen/}{Karen Macours} \\
 \href{https://theses.fr/2024EHES0027}{Online access: \faExternalLink} 
-\\ \href{https://www.dropbox.com/scl/fi/7yl7ri3en9vak8h2nyt44/R-sum-AHeimPhDV2.pdf?rlkey=w9k81hwyt6eu6390tgd1mqa6u&amp;dl=0}{Summary in French: \faExternalLink} </t>
-  </si>
-  <si>
-    <t>[\faAngleDoubleRight] \underline{Mémoire}:  \emph{Public sector as a shelter ? The impact of graduating in a recession on selection into public employment.}\\
-\underline{Directeur de mémoire}: \href{https://www.parisschoolofeconomics.eu/en/maurin-eric/}{Eric Maurin} \\
-\underline{Jury}: \href{https://sites.google.com/site/barbarapetrongolo/home}{Barbara Petrongolo}</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Évaluation des politiques publiques</t>
-  </si>
-  <si>
-    <t>Méthodes d'évaluations des politiques de santé</t>
-  </si>
-  <si>
-    <t>Évaluation des politiques de lutte contre la pauvreté</t>
-  </si>
-  <si>
-    <t>Reliance: Éxpérimentation aléatoire d'un programme d'activation de familles monoparentales au RSA longue durée</t>
-  </si>
-  <si>
-    <t>POSAJE: Éxpérimentation multi-bras pour favoriser l'accès aux modes d'accueil formels</t>
-  </si>
-  <si>
-    <t>ISAJE: Investissement social dans l'accueil du jeune enfant</t>
-  </si>
-  <si>
-    <t>MESAJE: Mesures des effets sociaux de l'accueil du jeune enfant</t>
-  </si>
-  <si>
-    <t>ADAJE: Aide à la décision pour l'accueil du jeune enfant</t>
-  </si>
-  <si>
-    <t>Bourse ERC - MADPART - avec Julien Combe. Déploiement d'algorithmes d'affectation des places en crèche et expérimentation aléatoire d'information détaillées aux familles sur leur fonctionnement. Analyse du rôle des options alternative des parents dans les choix</t>
-  </si>
-  <si>
-    <t>VISAJE: Valeurs individuelles et sociales de l'accueil du jeune enfant</t>
-  </si>
-  <si>
-    <t>Conférence de consensus: Le redoublement et ses alternatives</t>
-  </si>
-  <si>
-    <t>Les inégalités scolaires d'origines sociales</t>
-  </si>
-  <si>
-    <t>Recherche reproductible, intégration avec \LaTeX, présentations, sites web</t>
-  </si>
-  <si>
-    <t>Rapports et présentations</t>
-  </si>
-  <si>
-    <t>Formatage des données, programmation fonctionnelle</t>
-  </si>
-  <si>
-    <t>Contrôle de version, recherche collaborative</t>
-  </si>
-  <si>
-    <t>Manipulation de données et économétrie</t>
-  </si>
-  <si>
-    <t>Programmation orientée objet et science des données</t>
-  </si>
-  <si>
-    <t>Manipulation et visualisation de données ; économétrie, Machine learning</t>
-  </si>
-  <si>
-    <t>Paris School of Economics - EHESS, ED-465 Paris I, Panthéon Sorbonne</t>
-  </si>
-  <si>
-    <t>Marseille</t>
-  </si>
-  <si>
-    <t>Association française des économistes de la population</t>
-  </si>
-  <si>
-    <t>Jun 2024</t>
-  </si>
-  <si>
-    <t>Mai 2025</t>
-  </si>
-  <si>
-    <t>Conférence | AFEPOP 2025</t>
-  </si>
-  <si>
-    <t>Seminar | J-pal \&amp; IPP</t>
-  </si>
-  <si>
-    <t>Seminar | Public economics</t>
-  </si>
-  <si>
-    <t>OECD expert group |  ‘What standards of evidence are needed for policy design, implementation and evaluation’</t>
-  </si>
-  <si>
-    <t>International conference | Using educational research and innovation to address inequality and achievement gaps in education</t>
-  </si>
-  <si>
-    <t>Conference | Evaluating public policies</t>
-  </si>
-  <si>
-    <t>Seminar | education policies</t>
-  </si>
-  <si>
-    <t>Conférence | Social investment for the youths</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> \emph{Income support strategies to reduce inequalities : Insights from France}</t>
-  </si>
-  <si>
-    <t>\emph{Demand for international standards of evidence : thoughts from a French perspective}</t>
-  </si>
-  <si>
-    <t>Institut national des études teritoriales (INET)</t>
-  </si>
-  <si>
-    <t>Institut de la gestion publique et du développement économique (IGPDE)</t>
-  </si>
-  <si>
-    <t>École nationale supérieure de la sécurité sociale (EN3S)</t>
-  </si>
-  <si>
-    <t>Conduire l’évaluation des effets de la stratégie nationale de prévention et de lutte contre la pauvreté, sous la présidence de Louis Schweitzer.</t>
-  </si>
-  <si>
-    <t>Proposer des actions relevant de politiques publiques centrées sur le développement, l’épanouissement et les acquisitions du jeune enfant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nature Human Behaviour</t>
-  </si>
-  <si>
-    <t>{\bf Forthcoming}</t>
-  </si>
-  <si>
-    <t>{\bf R \&amp; R} European Economic Review</t>
-  </si>
-  <si>
-    <t>{\bf R \&amp; R} Nature Human Behaviour</t>
+ \href{https://www.dropbox.com/scl/fi/7yl7ri3en9vak8h2nyt44/R-sum-AHeimPhDV2.pdf?rlkey=w9k81hwyt6eu6390tgd1mqa6u&amp;dl=0}{Summary in French: \faExternalLink} </t>
+  </si>
+  <si>
+    <t>\href{https://www.ccomptes.fr/fr/actualites/la-cour-des-comptes-decerne-son-prix-de-these-2025}{Prix de thèse 2025}</t>
+  </si>
+  <si>
+    <t>A randomised controlled trial on the effect of administrative burden and information costs on social inequalities in early childcare access in France</t>
   </si>
 </sst>
 </file>
@@ -1520,13 +1539,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="51">
@@ -1543,7 +1562,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1594,6 +1613,254 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C59C71-C1DE-6345-8FA1-424DE87D1118}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
+    <col min="6" max="6" width="53.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="F3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="F5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" t="s">
+        <v>225</v>
+      </c>
+      <c r="G6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="F7" t="s">
+        <v>263</v>
+      </c>
+      <c r="G7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8">
+        <v>2013</v>
+      </c>
+      <c r="E8">
+        <v>2014</v>
+      </c>
+      <c r="F8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9">
+        <v>2014</v>
+      </c>
+      <c r="E9">
+        <v>2016</v>
+      </c>
+      <c r="F9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89004A4C-135E-AE46-AB58-A9B77E14C3A4}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1624,16 +1891,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E2" t="s">
         <v>100</v>
@@ -1674,7 +1941,7 @@
         <v>89</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E4" t="s">
         <v>98</v>
@@ -1705,7 +1972,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -1725,7 +1992,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
@@ -1745,7 +2012,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B8" t="s">
         <v>95</v>
@@ -1757,7 +2024,7 @@
         <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
@@ -1765,7 +2032,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B9" t="s">
         <v>92</v>
@@ -1777,7 +2044,7 @@
         <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
@@ -1785,7 +2052,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
         <v>93</v>
@@ -1805,7 +2072,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B11" t="s">
         <v>90</v>
@@ -1825,7 +2092,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B12" t="s">
         <v>87</v>
@@ -1851,7 +2118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A382872-5565-5645-A6BC-BA5C4FC5CD7B}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1967,7 +2234,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D77EE8B4-4BE1-2846-B95C-A1F9E8046A96}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="182.1640625" bestFit="1" customWidth="1"/>
@@ -1979,7 +2246,7 @@
     <col min="7" max="7" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -2005,7 +2272,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="8" t="s">
         <v>212</v>
       </c>
@@ -2021,17 +2288,17 @@
       <c r="E2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
-        <v>217</v>
-      </c>
       <c r="G2" s="8" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="8" t="s">
         <v>213</v>
       </c>
@@ -2047,17 +2314,17 @@
       <c r="E3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
-        <v>216</v>
-      </c>
       <c r="G3" s="8" t="s">
         <v>17</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="8" t="s">
         <v>214</v>
       </c>
@@ -2081,7 +2348,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="8" t="s">
         <v>215</v>
       </c>
@@ -2105,7 +2372,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="8" t="s">
         <v>215</v>
       </c>
@@ -2129,7 +2396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2138,7 +2405,7 @@
       <c r="F7" s="10"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="D11" s="1"/>
     </row>
   </sheetData>
@@ -2182,10 +2449,10 @@
         <v>241</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>193</v>
@@ -2194,7 +2461,7 @@
         <v>139</v>
       </c>
       <c r="F2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
@@ -2220,7 +2487,7 @@
         <v>188</v>
       </c>
       <c r="F3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
@@ -2246,7 +2513,7 @@
         <v>188</v>
       </c>
       <c r="F4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -2260,7 +2527,7 @@
         <v>241</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C5" t="s">
         <v>89</v>
@@ -2272,7 +2539,7 @@
         <v>139</v>
       </c>
       <c r="F5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
@@ -2286,7 +2553,7 @@
         <v>241</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C6" t="s">
         <v>89</v>
@@ -2298,7 +2565,7 @@
         <v>139</v>
       </c>
       <c r="F6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -2364,7 +2631,7 @@
         <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2375,7 +2642,7 @@
         <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2386,7 +2653,7 @@
         <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2397,7 +2664,7 @@
         <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2408,7 +2675,7 @@
         <v>146</v>
       </c>
       <c r="C6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2419,7 +2686,7 @@
         <v>148</v>
       </c>
       <c r="C7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2430,7 +2697,7 @@
         <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -3146,7 +3413,7 @@
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24" t="s">
-        <v>43</v>
+        <v>298</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>186</v>
@@ -3208,7 +3475,7 @@
         <v>186</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F4" s="24">
         <v>2024</v>
@@ -3256,16 +3523,16 @@
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24" t="s">
-        <v>162</v>
+        <v>304</v>
       </c>
       <c r="D6" s="24" t="s">
         <v>206</v>
       </c>
       <c r="E6" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>295</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>296</v>
       </c>
       <c r="G6" s="24" t="s">
         <v>204</v>
@@ -3335,7 +3602,7 @@
         <v>111</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F9" s="24">
         <v>2024</v>
@@ -3357,247 +3624,52 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C59C71-C1DE-6345-8FA1-424DE87D1118}">
-  <dimension ref="A1:H9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E029A835-6DB0-954E-9D59-8D00C5A8C135}">
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="5" max="5" width="26.5" customWidth="1"/>
-    <col min="6" max="6" width="53.5" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="102">
       <c r="A2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B2" t="s">
-        <v>226</v>
+        <v>303</v>
+      </c>
+      <c r="B2">
+        <v>2025</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="F2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="F3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="F4" t="s">
-        <v>221</v>
-      </c>
-      <c r="G4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="F5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G5" t="s">
-        <v>170</v>
-      </c>
-      <c r="H5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>263</v>
-      </c>
-      <c r="B6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="F6" t="s">
-        <v>225</v>
-      </c>
-      <c r="G6" t="s">
-        <v>170</v>
-      </c>
-      <c r="H6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>265</v>
-      </c>
-      <c r="B7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="F7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G7" t="s">
-        <v>170</v>
-      </c>
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D8">
-        <v>2013</v>
-      </c>
-      <c r="E8">
-        <v>2014</v>
-      </c>
-      <c r="F8" t="s">
-        <v>223</v>
-      </c>
-      <c r="G8" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>267</v>
-      </c>
-      <c r="B9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9">
-        <v>2014</v>
-      </c>
-      <c r="E9">
-        <v>2016</v>
-      </c>
-      <c r="F9" t="s">
-        <v>224</v>
-      </c>
-      <c r="G9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H9" t="s">
-        <v>232</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="D2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/ArthurHeimCareerDataFr.xlsx
+++ b/Data/ArthurHeimCareerDataFr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurheim/Library/CloudStorage/Dropbox/Travail_encrypted_decrypted/PHD/career/Data_DrivenResume/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C25AB6-A7B2-084D-96FB-891C2F6CA225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46BE8E20-A326-A248-B527-68EC8EE33917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4700" yWindow="3200" windowWidth="27240" windowHeight="19200" activeTab="7" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
+    <workbookView xWindow="4920" yWindow="600" windowWidth="27240" windowHeight="19200" activeTab="10" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
   </bookViews>
   <sheets>
     <sheet name="education" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="299">
   <si>
     <t>Degree</t>
   </si>
@@ -326,27 +326,18 @@
     <t>France Stratégie</t>
   </si>
   <si>
-    <t xml:space="preserve"> \emph{L'apport des évaluations des investissements sociaux dans la jeunesse}</t>
-  </si>
-  <si>
     <t>Paris</t>
   </si>
   <si>
     <t>LIEPP (Sciences Po)</t>
   </si>
   <si>
-    <t xml:space="preserve"> \it{École à 2 ans : Une maternelle plus précoce et plus longue améliore-t-elle la réussite des élèves ?}</t>
-  </si>
-  <si>
     <t xml:space="preserve"> OECD \&amp;  US institute for Education Sciences (IES)</t>
   </si>
   <si>
     <t>Association française de sciences économique \&amp; DG Trésor</t>
   </si>
   <si>
-    <t xml:space="preserve"> \emph{Quand la scolarisation à 2 ans n'apporte pas les effets attendus : Analyse quasi-expérimentales à partir du panel 2007}</t>
-  </si>
-  <si>
     <t>OECD</t>
   </si>
   <si>
@@ -354,15 +345,6 @@
   </si>
   <si>
     <t>Paris I Sorbonne</t>
-  </si>
-  <si>
-    <t>\emph{Rage against the matching}</t>
-  </si>
-  <si>
-    <t>\emph{Tax burden on the poor}</t>
-  </si>
-  <si>
-    <t>\emph{Welfare-to-What?}</t>
   </si>
   <si>
     <t>sep 2016</t>
@@ -612,9 +594,6 @@
     <t>GalitzineHeim2024</t>
   </si>
   <si>
-    <t>CarbucciaEtAl2024</t>
-  </si>
-  <si>
     <t>Rage against the matching:
  fairness and inequalities in a market design experiment of daycare assignments in France</t>
   </si>
@@ -628,9 +607,6 @@
   <si>
     <t>Tax burden on the poor
 Single mothers' optimisation behaviours following an experimental activation programme in France</t>
-  </si>
-  <si>
-    <t>multi1002024</t>
   </si>
   <si>
     <t xml:space="preserve">\href{https://theses.fr/2024EHES0027}{Online access: \faExternalLink} 
@@ -696,10 +672,6 @@
 \\ \href{https://www.dropbox.com/scl/fi/9dbpmcefmout7rwrwqvt6/TaxBurdenEnShort.pdf?rlkey=omrpuo36dge0phkd2havhxo5p&amp;dl=0}{Slides: \faExternalLink}</t>
   </si>
   <si>
-    <t>Étude randomisée à plusieurs bras en Ile de France  mesurant les effets de la mise à disposition d'informations et d'un soutien administratif à des  femmes enceintes pour faciliter l'accès  à des services de garde des jeunes enfants.
-\\ \href{https://osf.io/rh7eb/?view_only=ef7409ac646544eaac946374de134892}{Pre-print and replication material: \faExternalLink}</t>
-  </si>
-  <si>
     <t>Avec Alexandra Galitzine</t>
   </si>
   <si>
@@ -948,12 +920,6 @@
     <t>Conférence | Social investment for the youths</t>
   </si>
   <si>
-    <t xml:space="preserve"> \emph{Income support strategies to reduce inequalities : Insights from France}</t>
-  </si>
-  <si>
-    <t>\emph{Demand for international standards of evidence : thoughts from a French perspective}</t>
-  </si>
-  <si>
     <t>Institut national des études teritoriales (INET)</t>
   </si>
   <si>
@@ -972,13 +938,7 @@
     <t xml:space="preserve"> Nature Human Behaviour</t>
   </si>
   <si>
-    <t>{\bf Forthcoming}</t>
-  </si>
-  <si>
     <t>{\bf R \&amp; R} European Economic Review</t>
-  </si>
-  <si>
-    <t>{\bf R \&amp; R} Nature Human Behaviour</t>
   </si>
   <si>
     <t>Social investment and the changing face of poverty: Essays on the design and evaluation of family and social policies in France</t>
@@ -1004,6 +964,28 @@
   </si>
   <si>
     <t>A randomised controlled trial on the effect of administrative burden and information costs on social inequalities in early childcare access in France</t>
+  </si>
+  <si>
+    <t>CarbucciaEtAl2025</t>
+  </si>
+  <si>
+    <t>Étude randomisée à plusieurs bras en Ile de France  mesurant les effets de la mise à disposition d'informations et d'un soutien administratif à des  femmes enceintes pour faciliter l'accès  à des services de garde des jeunes enfants.
+\\ \href{https://www.nature.com/articles/s41562-025-02293-4}{\faExternalLink}</t>
+  </si>
+  <si>
+    <t>Nature Human Behaviour</t>
+  </si>
+  <si>
+    <t>multi1002025</t>
+  </si>
+  <si>
+    <t>Conférence | Numérique en commun[s] 2025</t>
+  </si>
+  <si>
+    <t>Numérique en commun[s]</t>
+  </si>
+  <si>
+    <t>Oct 2025</t>
   </si>
 </sst>
 </file>
@@ -1533,24 +1515,24 @@
     </row>
     <row r="2" spans="1:5" ht="119">
       <c r="A2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="51">
       <c r="A3" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -1562,40 +1544,40 @@
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B6">
         <v>2007</v>
@@ -1604,7 +1586,7 @@
         <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1605,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
@@ -1644,82 +1626,82 @@
         <v>15</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G2" t="s">
         <v>165</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="F2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G2" t="s">
-        <v>171</v>
-      </c>
       <c r="H2" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F4" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H4" t="s">
         <v>29</v>
@@ -1727,77 +1709,77 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F5" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="G5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H5" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="G6" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H6" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F7" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="G7" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H7" t="s">
         <v>29</v>
@@ -1805,13 +1787,13 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D8">
         <v>2013</v>
@@ -1820,24 +1802,24 @@
         <v>2014</v>
       </c>
       <c r="F8" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G8" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H8" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D9">
         <v>2014</v>
@@ -1846,13 +1828,13 @@
         <v>2016</v>
       </c>
       <c r="F9" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G9" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H9" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -1862,7 +1844,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89004A4C-135E-AE46-AB58-A9B77E14C3A4}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="73.5" customWidth="1"/>
@@ -1890,81 +1872,71 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="E2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="E4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>17</v>
       </c>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" t="s">
-        <v>99</v>
+        <v>268</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -1972,19 +1944,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
@@ -1992,18 +1961,15 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" t="s">
         <v>100</v>
       </c>
       <c r="F7" t="s">
@@ -2012,19 +1978,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" t="s">
-        <v>288</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
@@ -2032,19 +1995,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B9" t="s">
         <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" t="s">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
@@ -2052,39 +2012,33 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
         <v>93</v>
       </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
       <c r="D10" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F11" t="s">
         <v>19</v>
@@ -2092,27 +2046,41 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B13" t="s">
         <v>87</v>
       </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C13" t="s">
         <v>88</v>
       </c>
-      <c r="F12" t="s">
+      <c r="D13" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F12">
-    <sortCondition descending="1" ref="D4:D12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F13">
+    <sortCondition descending="1" ref="D5:D13"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2148,28 +2116,28 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="18" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>66</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F2" s="18"/>
       <c r="G2" s="18" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -2184,18 +2152,18 @@
         <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="18" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
         <v>70</v>
@@ -2204,18 +2172,18 @@
         <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="18" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C5" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D5" t="s">
         <v>72</v>
@@ -2224,7 +2192,7 @@
         <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -2274,16 +2242,16 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="8" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>16</v>
@@ -2295,15 +2263,15 @@
         <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="8" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>32</v>
@@ -2321,15 +2289,15 @@
         <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="8" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>32</v>
@@ -2350,10 +2318,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="8" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>32</v>
@@ -2374,10 +2342,10 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="8" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>32</v>
@@ -2446,22 +2414,22 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C2" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F2" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
@@ -2472,22 +2440,22 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F3" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
@@ -2498,22 +2466,22 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
         <v>87</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F4" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -2524,22 +2492,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B5" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F5" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
@@ -2550,22 +2518,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F6" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -2614,90 +2582,90 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2712,189 +2680,189 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
         <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
         <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B15" t="s">
         <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B16" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2963,7 +2931,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -2989,7 +2957,7 @@
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -3012,7 +2980,7 @@
         <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -3032,13 +3000,13 @@
         <v>2024</v>
       </c>
       <c r="F5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
@@ -3052,7 +3020,7 @@
         <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E6">
         <v>2024</v>
@@ -3112,19 +3080,19 @@
     </row>
     <row r="9" spans="1:8" ht="24" customHeight="1">
       <c r="B9" s="16" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E9">
         <v>2024</v>
       </c>
       <c r="F9" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -3182,7 +3150,7 @@
       </c>
       <c r="C2" s="24"/>
       <c r="D2" s="24" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E2" s="24">
         <v>2024</v>
@@ -3194,7 +3162,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="85">
@@ -3214,13 +3182,13 @@
         <v>2024</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G3" s="24" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="119">
@@ -3244,7 +3212,7 @@
         <v>17</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="221">
@@ -3264,25 +3232,25 @@
         <v>2024</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G5" s="24" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="221">
       <c r="A6" s="24"/>
       <c r="B6" s="24" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E6" s="24">
         <v>2024</v>
@@ -3346,19 +3314,19 @@
     <row r="9" spans="1:8" ht="153">
       <c r="A9" s="24"/>
       <c r="B9" s="26" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E9" s="24">
         <v>2024</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G9" s="24" t="s">
         <v>17</v>
@@ -3380,7 +3348,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17">
       <c r="A1" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>52</v>
@@ -3409,133 +3377,133 @@
     </row>
     <row r="2" spans="1:9" ht="136">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F2" s="24">
         <v>2024</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="H2" s="24" t="s">
         <v>17</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="306">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F3" s="24">
         <v>2024</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="H3" s="24" t="s">
         <v>17</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="170">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="F4" s="24">
         <v>2024</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H4" s="24" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="272">
       <c r="A5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F5" s="24">
         <v>2024</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="H5" s="24" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="204">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="187">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>292</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>295</v>
+        <v>283</v>
+      </c>
+      <c r="F6" s="24">
+        <v>2025</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>204</v>
+        <v>293</v>
       </c>
       <c r="H6" s="24" t="s">
         <v>17</v>
@@ -3553,7 +3521,7 @@
         <v>77</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F7" s="24" t="s">
         <v>63</v>
@@ -3574,10 +3542,10 @@
         <v>85</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F8" s="24">
         <v>2026</v>
@@ -3592,23 +3560,23 @@
     </row>
     <row r="9" spans="1:9" ht="102">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="B9" s="24"/>
       <c r="C9" s="26" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F9" s="24">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>17</v>
@@ -3647,19 +3615,19 @@
     </row>
     <row r="2" spans="1:5" ht="102">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="B2">
         <v>2025</v>
       </c>
       <c r="C2" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:5">

--- a/Data/ArthurHeimCareerDataFr.xlsx
+++ b/Data/ArthurHeimCareerDataFr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurheim/Library/CloudStorage/Dropbox/Travail_encrypted_decrypted/PHD/career/Data_DrivenResume/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46BE8E20-A326-A248-B527-68EC8EE33917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA5FB91-E8F6-AC4F-97CF-810705029CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="600" windowWidth="27240" windowHeight="19200" activeTab="10" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
+    <workbookView xWindow="4920" yWindow="600" windowWidth="27240" windowHeight="19200" activeTab="9" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
   </bookViews>
   <sheets>
     <sheet name="education" sheetId="1" r:id="rId1"/>
@@ -836,9 +836,6 @@
     <t>Reliance: Éxpérimentation aléatoire d'un programme d'activation de familles monoparentales au RSA longue durée</t>
   </si>
   <si>
-    <t>POSAJE: Éxpérimentation multi-bras pour favoriser l'accès aux modes d'accueil formels</t>
-  </si>
-  <si>
     <t>ISAJE: Investissement social dans l'accueil du jeune enfant</t>
   </si>
   <si>
@@ -986,6 +983,9 @@
   </si>
   <si>
     <t>Oct 2025</t>
+  </si>
+  <si>
+    <t>"Baby steps": Éxpérimentation multi-bras pour favoriser l'accès aux modes d'accueil formels</t>
   </si>
 </sst>
 </file>
@@ -1521,13 +1521,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="51">
@@ -1657,7 +1657,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>298</v>
       </c>
       <c r="B3" t="s">
         <v>220</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" t="s">
         <v>218</v>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B5" t="s">
         <v>218</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B6" t="s">
         <v>218</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B7" t="s">
         <v>218</v>
@@ -1776,7 +1776,7 @@
         <v>186</v>
       </c>
       <c r="F7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G7" t="s">
         <v>164</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B8" t="s">
         <v>219</v>
@@ -1813,7 +1813,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B9" t="s">
         <v>219</v>
@@ -1873,16 +1873,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>245</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
@@ -1892,16 +1892,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -1936,7 +1936,7 @@
         <v>88</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B8" t="s">
         <v>94</v>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B9" t="s">
         <v>92</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B10" t="s">
         <v>90</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B11" t="s">
         <v>91</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B12" t="s">
         <v>89</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B13" t="s">
         <v>87</v>
@@ -2417,7 +2417,7 @@
         <v>232</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s">
         <v>245</v>
@@ -2455,7 +2455,7 @@
         <v>180</v>
       </c>
       <c r="F3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
@@ -2481,7 +2481,7 @@
         <v>180</v>
       </c>
       <c r="F4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -2495,7 +2495,7 @@
         <v>232</v>
       </c>
       <c r="B5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
         <v>88</v>
@@ -2521,7 +2521,7 @@
         <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C6" t="s">
         <v>88</v>
@@ -2599,7 +2599,7 @@
         <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2610,7 +2610,7 @@
         <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2621,7 +2621,7 @@
         <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2632,7 +2632,7 @@
         <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2643,7 +2643,7 @@
         <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2654,7 +2654,7 @@
         <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2665,7 +2665,7 @@
         <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>178</v>
@@ -3443,7 +3443,7 @@
         <v>178</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F4" s="24">
         <v>2024</v>
@@ -3487,23 +3487,23 @@
     </row>
     <row r="6" spans="1:9" ht="187">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D6" s="24" t="s">
         <v>197</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="24">
         <v>2025</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H6" s="24" t="s">
         <v>17</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="9" spans="1:9" ht="102">
       <c r="A9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B9" s="24"/>
       <c r="C9" s="26" t="s">
@@ -3570,7 +3570,7 @@
         <v>105</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F9" s="24">
         <v>2025</v>
@@ -3615,19 +3615,19 @@
     </row>
     <row r="2" spans="1:5" ht="102">
       <c r="A2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B2">
         <v>2025</v>
       </c>
       <c r="C2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2" t="s">
         <v>286</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:5">
